--- a/data/trans_orig/IQ19B_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_M-Edad-trans_orig.xlsx
@@ -9662,7 +9662,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10247,12 +10247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10262,12 +10262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -10878,12 +10878,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -11217,12 +11217,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -11550,12 +11550,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>32483</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12342,12 +12342,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12362,12 +12362,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>70286</t>
+          <t>69981</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>84903</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12903,12 +12903,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -13180,12 +13180,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13513,12 +13513,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>51326</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>52028</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>62293</t>
+          <t>62572</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13826,12 +13826,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>107714</t>
+          <t>107062</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>121822</t>
+          <t>121358</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13861,12 +13861,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14115,12 +14115,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14130,12 +14130,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -14150,12 +14150,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14165,12 +14165,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14185,12 +14185,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14200,12 +14200,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -14226,12 +14226,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -14296,12 +14296,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -14311,12 +14311,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -14337,12 +14337,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -14448,12 +14448,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14463,12 +14463,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14483,12 +14483,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -14518,12 +14518,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -14559,12 +14559,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -14594,12 +14594,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14609,12 +14609,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14740,12 +14740,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -14892,12 +14892,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14907,12 +14907,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14927,12 +14927,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15053,12 +15053,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15088,12 +15088,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -15184,12 +15184,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>462</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -15225,12 +15225,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>101404</t>
+          <t>101748</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>116985</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -15260,12 +15260,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>107073</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>124282</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>213893</t>
+          <t>213678</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>237512</t>
+          <t>237679</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -15310,12 +15310,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -17250,7 +17250,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17285,7 +17285,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17426,12 +17426,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17441,12 +17441,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -17467,12 +17467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17482,12 +17482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17502,12 +17502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -17517,12 +17517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17537,12 +17537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17552,12 +17552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -17613,12 +17613,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17628,12 +17628,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -17648,12 +17648,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17663,12 +17663,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -17774,12 +17774,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18390,12 +18390,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18405,12 +18405,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18425,12 +18425,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37108</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18440,12 +18440,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18764,12 +18764,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18779,12 +18779,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -18805,12 +18805,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18855,12 +18855,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18890,12 +18890,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -18916,12 +18916,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -18931,12 +18931,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -19001,12 +19001,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -19027,12 +19027,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19042,12 +19042,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19062,12 +19062,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19077,12 +19077,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19097,12 +19097,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -19138,12 +19138,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -19153,12 +19153,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -19173,12 +19173,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19188,12 +19188,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19733,7 +19733,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -19804,12 +19804,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55336</t>
+          <t>55345</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>52569</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19854,12 +19854,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19874,12 +19874,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>88743</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>104544</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19889,12 +19889,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -20289,12 +20289,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -20304,12 +20304,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -20324,12 +20324,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -20339,12 +20339,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -20365,12 +20365,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -20400,12 +20400,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -20415,12 +20415,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -20435,12 +20435,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -20450,12 +20450,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -20476,12 +20476,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -20511,12 +20511,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -20546,12 +20546,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -20561,12 +20561,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -20587,12 +20587,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -20602,12 +20602,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -20622,12 +20622,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -20657,12 +20657,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -20672,12 +20672,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -21197,7 +21197,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -21253,12 +21253,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>48902</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -21268,12 +21268,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -21288,12 +21288,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>51284</t>
+          <t>51366</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>62489</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -21303,12 +21303,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -21323,12 +21323,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>90609</t>
+          <t>91828</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>107704</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -21521,7 +21521,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -21592,12 +21592,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -21607,12 +21607,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -21627,12 +21627,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -21642,12 +21642,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -21662,12 +21662,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -21677,12 +21677,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -21703,12 +21703,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -21718,12 +21718,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -21753,12 +21753,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -21773,12 +21773,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21788,12 +21788,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -21814,12 +21814,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -21829,12 +21829,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -21849,12 +21849,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -21864,12 +21864,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -21884,12 +21884,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -21899,12 +21899,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -21925,12 +21925,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -21940,12 +21940,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -21960,12 +21960,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21975,12 +21975,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -21995,12 +21995,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -22010,12 +22010,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -22036,12 +22036,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -22051,12 +22051,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -22071,12 +22071,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -22086,12 +22086,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -22106,12 +22106,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -22121,12 +22121,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -22263,7 +22263,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -22369,12 +22369,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -22485,7 +22485,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22550,12 +22550,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -22626,12 +22626,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -22641,12 +22641,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>98929</t>
+          <t>99802</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>117694</t>
+          <t>118184</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -22717,12 +22717,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -22737,12 +22737,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111909</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>130236</t>
+          <t>130364</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>216039</t>
+          <t>217414</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>241685</t>
+          <t>243293</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -22787,12 +22787,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -23611,7 +23611,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -23626,7 +23626,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -23696,7 +23696,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -24651,7 +24651,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -24757,12 +24757,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -24772,12 +24772,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -24792,12 +24792,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -24807,12 +24807,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -24833,12 +24833,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -24848,12 +24848,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -24868,12 +24868,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -24883,12 +24883,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -24903,12 +24903,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -24918,12 +24918,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -24944,12 +24944,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -24959,12 +24959,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -25014,12 +25014,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -25029,12 +25029,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -25060,7 +25060,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -25145,7 +25145,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -25166,12 +25166,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -25181,12 +25181,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -25201,12 +25201,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -25236,12 +25236,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -25251,12 +25251,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -25393,7 +25393,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -25408,7 +25408,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -25458,12 +25458,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -25473,12 +25473,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25504,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -25650,7 +25650,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -25832,12 +25832,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -25847,12 +25847,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -25867,12 +25867,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -25882,12 +25882,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -25902,12 +25902,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>37505</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50840</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,49%</t>
         </is>
       </c>
     </row>
@@ -26065,7 +26065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -26135,7 +26135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -26176,7 +26176,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -26241,12 +26241,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -26282,12 +26282,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -26297,12 +26297,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -26317,12 +26317,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -26332,12 +26332,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -26352,12 +26352,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -26367,12 +26367,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -26393,12 +26393,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -26408,12 +26408,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -26428,12 +26428,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -26463,12 +26463,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -26478,12 +26478,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -26504,12 +26504,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -26539,12 +26539,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -26554,12 +26554,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -26574,12 +26574,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -26589,12 +26589,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -26615,12 +26615,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -26650,12 +26650,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -26665,12 +26665,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -26685,12 +26685,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -26700,12 +26700,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -26796,12 +26796,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>383</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -26983,12 +26983,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -26998,12 +26998,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -27033,12 +27033,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -27099,7 +27099,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -27129,12 +27129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>808</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -27144,12 +27144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -27175,7 +27175,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -27240,12 +27240,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -27281,12 +27281,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>35828</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>49877</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -27296,12 +27296,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -27316,12 +27316,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -27331,12 +27331,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -27351,12 +27351,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>64725</t>
+          <t>65677</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>88780</t>
+          <t>88930</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27366,12 +27366,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -27620,12 +27620,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -27655,12 +27655,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -27670,12 +27670,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -27705,12 +27705,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -27731,12 +27731,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -27746,12 +27746,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -27766,12 +27766,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -27781,7 +27781,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -27801,12 +27801,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>30803</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -27816,12 +27816,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -27842,12 +27842,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -27857,12 +27857,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -27877,12 +27877,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -27892,12 +27892,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -27912,12 +27912,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -27927,12 +27927,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -27953,12 +27953,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -27968,12 +27968,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -27988,12 +27988,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -28023,12 +28023,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -28038,12 +28038,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -28064,12 +28064,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -28079,12 +28079,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -28099,12 +28099,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -28119,7 +28119,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -28134,12 +28134,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -28180,7 +28180,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -28215,7 +28215,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -28245,12 +28245,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -28260,12 +28260,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -28291,7 +28291,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -28356,12 +28356,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -28371,12 +28371,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -28397,12 +28397,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>399</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -28412,12 +28412,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -28432,12 +28432,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -28447,12 +28447,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -28467,12 +28467,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -28482,12 +28482,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -28508,12 +28508,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -28523,12 +28523,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -28543,12 +28543,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -28558,12 +28558,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -28593,12 +28593,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28624,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -28694,7 +28694,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -28730,12 +28730,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>45712</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -28745,12 +28745,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>67563</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>89814</t>
+          <t>90360</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -28780,12 +28780,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -28800,12 +28800,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>118958</t>
+          <t>118399</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>146110</t>
+          <t>146238</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -28815,12 +28815,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -28978,7 +28978,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -29043,12 +29043,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -29069,12 +29069,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -29104,12 +29104,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -29119,12 +29119,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -29139,12 +29139,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -29154,12 +29154,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -29180,12 +29180,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -29195,12 +29195,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -29215,12 +29215,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -29230,12 +29230,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -29250,12 +29250,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -29265,12 +29265,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -29306,12 +29306,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -29326,12 +29326,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -29341,12 +29341,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -29361,12 +29361,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -29376,12 +29376,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -29402,12 +29402,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -29437,12 +29437,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -29452,12 +29452,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -29472,12 +29472,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29487,12 +29487,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -29513,12 +29513,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -29528,12 +29528,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -29548,12 +29548,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -29563,12 +29563,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -29583,12 +29583,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -29598,12 +29598,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -29624,12 +29624,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29659,12 +29659,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>825</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29674,12 +29674,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29694,12 +29694,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -29740,7 +29740,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -29755,7 +29755,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -29770,12 +29770,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29785,12 +29785,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29805,12 +29805,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -29846,12 +29846,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29861,12 +29861,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29881,12 +29881,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29896,12 +29896,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29931,12 +29931,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -29957,12 +29957,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29972,12 +29972,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29992,12 +29992,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -30007,12 +30007,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -30027,12 +30027,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -30068,12 +30068,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -30083,12 +30083,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -30123,7 +30123,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -30153,12 +30153,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30179,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>104391</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>128525</t>
+          <t>129327</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -30194,12 +30194,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -30214,12 +30214,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>129618</t>
+          <t>129138</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>156970</t>
+          <t>157613</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -30229,12 +30229,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>238816</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>280846</t>
+          <t>278178</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
